--- a/Project/outputs/tables/table_var_metrics_h10.xlsx
+++ b/Project/outputs/tables/table_var_metrics_h10.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01014728011057196</v>
+        <v>0.01060975217866216</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05522622639018436</v>
+        <v>0.0541950777254756</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1007337089090437</v>
+        <v>0.1030036512880109</v>
       </c>
       <c r="E2" t="n">
-        <v>32.59993190426994</v>
+        <v>31.09283051866673</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4620573355817875</v>
+        <v>0.4468802698145025</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005510572133178346</v>
+        <v>0.006701393679230809</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04730060139926567</v>
+        <v>0.05355201723052324</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07423322795876754</v>
+        <v>0.08186204052691827</v>
       </c>
       <c r="E3" t="n">
-        <v>33.88974936917149</v>
+        <v>31.4404291781107</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4435075885328836</v>
+        <v>0.4367622259696459</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004879578634187827</v>
+        <v>0.007628605655117836</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04411998802734672</v>
+        <v>0.05640318791640315</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0698539808041591</v>
+        <v>0.08734188946386399</v>
       </c>
       <c r="E4" t="n">
-        <v>27.12270671895173</v>
+        <v>34.08042473694281</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4789207419898819</v>
+        <v>0.4350758853288364</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006414766221804905</v>
+        <v>0.00486995095357275</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05404712971458685</v>
+        <v>0.04261341069282162</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08009223571486131</v>
+        <v>0.06978503387957012</v>
       </c>
       <c r="E5" t="n">
-        <v>32.35421639736992</v>
+        <v>25.55824548448197</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4603709949409781</v>
+        <v>0.4772344013490725</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002278740063162349</v>
+        <v>0.002531151408939288</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03420710593864974</v>
+        <v>0.03594620130635173</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0477361504853748</v>
+        <v>0.05031054967836555</v>
       </c>
       <c r="E6" t="n">
-        <v>19.71450681124509</v>
+        <v>20.70230535719237</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4974704890387858</v>
+        <v>0.4907251264755481</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,23 +653,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00302894195131993</v>
+        <v>0.005098524775011127</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04071571105497655</v>
+        <v>0.04447271761951302</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05503582425402503</v>
+        <v>0.0714039548975484</v>
       </c>
       <c r="E7" t="n">
-        <v>21.56304802022735</v>
+        <v>24.36869812808487</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4519392917369309</v>
+        <v>0.4401349072512648</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00902549290687083</v>
+        <v>0.003000190737024782</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05545450105486033</v>
+        <v>0.03977845691761409</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09500259421126789</v>
+        <v>0.05477399690569223</v>
       </c>
       <c r="E8" t="n">
-        <v>26.35769422646293</v>
+        <v>21.27424436268294</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4704890387858348</v>
+        <v>0.4553119730185498</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003125376644012701</v>
+        <v>0.002851434154963515</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04029626670392743</v>
+        <v>0.03684315816587646</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05590506814245647</v>
+        <v>0.0533988216626876</v>
       </c>
       <c r="E9" t="n">
-        <v>21.0598521119117</v>
+        <v>22.62181554306886</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4873524451939292</v>
+        <v>0.4671163575042159</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.005551343583138606</v>
+        <v>0.005411375442815282</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04642094128547471</v>
+        <v>0.04547552844682237</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07232409880999449</v>
+        <v>0.07148499228783214</v>
       </c>
       <c r="E10" t="n">
-        <v>26.83271319495127</v>
+        <v>26.3923741636539</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4690134907251265</v>
+        <v>0.4561551433389545</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.002975897026256895</v>
+        <v>0.002952593088796222</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03761158125021045</v>
+        <v>0.03702461116428681</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05455178297963225</v>
+        <v>0.0543377685297825</v>
       </c>
       <c r="E11" t="n">
-        <v>24.33504858113979</v>
+        <v>23.61281905574247</v>
       </c>
       <c r="F11" t="n">
-        <v>0.464508094645081</v>
+        <v>0.47125</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.002353069061726336</v>
+        <v>0.003228468684318897</v>
       </c>
       <c r="C12" t="n">
-        <v>0.03200200448080189</v>
+        <v>0.03767367306230766</v>
       </c>
       <c r="D12" t="n">
-        <v>0.048508443200399</v>
+        <v>0.05681961531301402</v>
       </c>
       <c r="E12" t="n">
-        <v>26.07786509649164</v>
+        <v>24.78313789608564</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4682440846824408</v>
+        <v>0.47125</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.00242270005224461</v>
+        <v>0.002939652580568508</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03210461944991243</v>
+        <v>0.03591170852689707</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04922093103797012</v>
+        <v>0.05421856306255735</v>
       </c>
       <c r="E13" t="n">
-        <v>29.93198562104177</v>
+        <v>24.85931564637347</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4707347447073474</v>
+        <v>0.47375</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.003083510348484896</v>
+        <v>0.002502315505643708</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03675119422049303</v>
+        <v>0.032392323829343</v>
       </c>
       <c r="D14" t="n">
-        <v>0.05552936474051271</v>
+        <v>0.0500231496973522</v>
       </c>
       <c r="E14" t="n">
-        <v>24.64791579950838</v>
+        <v>29.725831827476</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4919053549190536</v>
+        <v>0.4675</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.007730952898767971</v>
+        <v>0.007625907671563772</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04619290043765369</v>
+        <v>0.04640225664501917</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08792583749255943</v>
+        <v>0.08732644314045873</v>
       </c>
       <c r="E15" t="n">
-        <v>21.51190209613016</v>
+        <v>21.96008208202184</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4869240348692404</v>
+        <v>0.47625</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.006620130303580667</v>
+        <v>0.003795321037246374</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04783439254307318</v>
+        <v>0.040536400662242</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08136418317405188</v>
+        <v>0.06160617694068001</v>
       </c>
       <c r="E16" t="n">
-        <v>18.44801392467694</v>
+        <v>23.48553038325822</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5217932752179327</v>
+        <v>0.50125</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.003353537389813327</v>
+        <v>0.006401720328854142</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04193608153590341</v>
+        <v>0.04648306487641752</v>
       </c>
       <c r="D17" t="n">
-        <v>0.05790973484495786</v>
+        <v>0.08001075133289365</v>
       </c>
       <c r="E17" t="n">
-        <v>25.53707985301586</v>
+        <v>18.05246199165389</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4694894146948941</v>
+        <v>0.51625</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.002737723444627855</v>
+        <v>0.003063254996575782</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0354099734333146</v>
+        <v>0.03812333832352613</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05232325911702992</v>
+        <v>0.05534668008630492</v>
       </c>
       <c r="E18" t="n">
-        <v>24.47503811990871</v>
+        <v>29.9501125793992</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5068493150684932</v>
+        <v>0.46625</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.00390969006568782</v>
+        <v>0.004063654236695925</v>
       </c>
       <c r="C19" t="n">
-        <v>0.03873034341892034</v>
+        <v>0.03931842213625492</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06091669207338914</v>
+        <v>0.06246114351288042</v>
       </c>
       <c r="E19" t="n">
-        <v>24.37060613648915</v>
+        <v>24.55366143275134</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4850560398505604</v>
+        <v>0.48046875</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
